--- a/runs/experiments.xlsx
+++ b/runs/experiments.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upcomillas-my.sharepoint.com/personal/202111181_alu_comillas_edu/Documents/ICAI/Master/RLprof/Practicas/MiniGrid_Locked4RoomEnv/runs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_826CE3EED135690DA44FD929FBF3D78DA7B44F91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50799215-A9D6-4CBE-A291-B764F640E064}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-38510" yWindow="-2840" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="runs"/>
+    <sheet name="runs" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="129">
   <si>
     <t>run_id</t>
   </si>
@@ -386,9 +392,6 @@
   </si>
   <si>
     <t>runs/Apr18_23_11_20/best_model.zip</t>
-  </si>
-  <si>
-    <t>runs/Apr18_23_11_20/ppo_partialobs_final.pt</t>
   </si>
   <si>
     <t>ppo_fullobs_basereward_6rooms_Apr19_09_57_13</t>
@@ -409,8 +412,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -441,7 +446,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffff00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -462,16 +467,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -479,86 +484,75 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -569,10 +563,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -610,71 +604,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -702,7 +696,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -725,11 +719,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -738,13 +732,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -754,7 +748,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -763,7 +757,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -772,7 +766,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -780,10 +774,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -848,2520 +842,2406 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AL24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="19" width="16.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="19" width="23.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="19" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="20" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="20" width="8.862142857142858" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="21" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="20" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="20" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="22" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="20" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="20" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="20" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="22" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="22" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="22" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="22" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="22" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="22" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="22" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="22" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="20" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="23" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="23" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="20" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="23" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="23" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="21" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="19" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="19" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="21" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="21" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="19" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="23" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="21" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="19" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="19" width="17.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="19" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="19" width="13.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="20" width="12.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="12.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="12.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AG1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="4">
-        <v>42</v>
-      </c>
-      <c r="H2" s="4">
+      <c r="F2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="3">
+        <v>42</v>
+      </c>
+      <c r="H2" s="3">
         <v>19</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="3">
         <v>8</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>3000000</v>
       </c>
-      <c r="M2" s="6">
-        <v>0.00025</v>
-      </c>
-      <c r="N2" s="4">
+      <c r="M2" s="18">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N2" s="3">
         <v>512</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="3">
         <v>256</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="3">
         <v>4</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="5">
         <v>0.99</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="5">
         <v>0.95</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="5">
         <v>0.2</v>
       </c>
-      <c r="T2" s="6">
+      <c r="T2" s="5">
         <v>0.01</v>
       </c>
-      <c r="U2" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="V2" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="W2" s="6">
+      <c r="U2" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="W2" s="5">
         <v>0.3</v>
       </c>
-      <c r="X2" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="4">
+      <c r="X2" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" s="3">
         <v>512</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" t="s">
         <v>45</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" t="s">
         <v>45</v>
       </c>
-      <c r="AD2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE2" s="4">
+      <c r="AD2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE2" s="3">
         <v>12319304</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" t="s">
         <v>46</v>
       </c>
-      <c r="AG2" s="6"/>
-      <c r="AH2" s="4">
+      <c r="AG2" s="5"/>
+      <c r="AH2" s="3">
         <v>0</v>
       </c>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="4">
-        <v>42</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="F3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="3">
+        <v>42</v>
+      </c>
+      <c r="H3" s="3">
         <v>19</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="3">
         <v>8</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="3">
         <v>3000000</v>
       </c>
-      <c r="M3" s="6">
-        <v>0.00025</v>
-      </c>
-      <c r="N3" s="4">
+      <c r="M3" s="18">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N3" s="3">
         <v>512</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3" s="3">
         <v>256</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="3">
         <v>4</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="5">
         <v>0.99</v>
       </c>
-      <c r="R3" s="6">
+      <c r="R3" s="5">
         <v>0.95</v>
       </c>
-      <c r="S3" s="6">
+      <c r="S3" s="5">
         <v>0.2</v>
       </c>
-      <c r="T3" s="6">
+      <c r="T3" s="5">
         <v>0.01</v>
       </c>
-      <c r="U3" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="V3" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="W3" s="6">
+      <c r="U3" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="V3" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="W3" s="5">
         <v>0.3</v>
       </c>
-      <c r="X3" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA3" s="4">
+      <c r="X3" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA3" s="3">
         <v>512</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AB3" t="s">
         <v>45</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AC3" t="s">
         <v>45</v>
       </c>
-      <c r="AD3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE3" s="4">
+      <c r="AD3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE3" s="3">
         <v>12319304</v>
       </c>
-      <c r="AF3" s="1" t="s">
+      <c r="AF3" t="s">
         <v>46</v>
       </c>
-      <c r="AG3" s="6"/>
-      <c r="AH3" s="4">
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="3">
         <v>0</v>
       </c>
-      <c r="AI3" s="1"/>
-      <c r="AJ3" s="1"/>
-      <c r="AK3" s="1"/>
-      <c r="AL3" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="4">
-        <v>42</v>
-      </c>
-      <c r="H4" s="4">
+      <c r="F4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="3">
+        <v>42</v>
+      </c>
+      <c r="H4" s="3">
         <v>19</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="3">
         <v>8</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>15000000</v>
       </c>
-      <c r="M4" s="6">
-        <v>0.00025</v>
-      </c>
-      <c r="N4" s="4">
+      <c r="M4" s="18">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N4" s="3">
         <v>512</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="3">
         <v>256</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4" s="3">
         <v>4</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="5">
         <v>0.99</v>
       </c>
-      <c r="R4" s="6">
+      <c r="R4" s="5">
         <v>0.95</v>
       </c>
-      <c r="S4" s="6">
+      <c r="S4" s="5">
         <v>0.2</v>
       </c>
-      <c r="T4" s="6">
+      <c r="T4" s="5">
         <v>0.05</v>
       </c>
-      <c r="U4" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="V4" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="W4" s="6">
+      <c r="U4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="V4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="W4" s="5">
         <v>0.3</v>
       </c>
-      <c r="X4" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA4" s="4">
+      <c r="X4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA4" s="3">
         <v>512</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AB4" t="s">
         <v>45</v>
       </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AC4" t="s">
         <v>45</v>
       </c>
-      <c r="AD4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE4" s="4">
+      <c r="AD4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE4" s="3">
         <v>12319304</v>
       </c>
-      <c r="AF4" s="1" t="s">
+      <c r="AF4" t="s">
         <v>46</v>
       </c>
-      <c r="AG4" s="6">
+      <c r="AG4" s="5">
         <v>0.06</v>
       </c>
-      <c r="AH4" s="6">
-        <v>0.005</v>
-      </c>
-      <c r="AI4" s="1" t="s">
+      <c r="AH4" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AI4" t="s">
         <v>51</v>
       </c>
-      <c r="AJ4" s="1" t="s">
+      <c r="AJ4" t="s">
         <v>52</v>
       </c>
-      <c r="AK4" s="1"/>
-      <c r="AL4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="4">
-        <v>42</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="F5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="3">
+        <v>42</v>
+      </c>
+      <c r="H5" s="3">
         <v>19</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>8</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>15000000</v>
       </c>
-      <c r="M5" s="6">
-        <v>0.00025</v>
-      </c>
-      <c r="N5" s="4">
+      <c r="M5" s="18">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N5" s="3">
         <v>1024</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="3">
         <v>256</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5" s="3">
         <v>4</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="5">
         <v>0.99</v>
       </c>
-      <c r="R5" s="6">
+      <c r="R5" s="5">
         <v>0.95</v>
       </c>
-      <c r="S5" s="6">
+      <c r="S5" s="5">
         <v>0.2</v>
       </c>
-      <c r="T5" s="6">
+      <c r="T5" s="5">
         <v>0.05</v>
       </c>
-      <c r="U5" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="V5" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="W5" s="6">
+      <c r="U5" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="V5" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="W5" s="5">
         <v>0.3</v>
       </c>
-      <c r="X5" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA5" s="4">
+      <c r="X5" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA5" s="3">
         <v>512</v>
       </c>
-      <c r="AB5" s="1" t="s">
+      <c r="AB5" t="s">
         <v>45</v>
       </c>
-      <c r="AC5" s="1" t="s">
+      <c r="AC5" t="s">
         <v>45</v>
       </c>
-      <c r="AD5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE5" s="4">
+      <c r="AD5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE5" s="3">
         <v>12319304</v>
       </c>
-      <c r="AF5" s="1" t="s">
+      <c r="AF5" t="s">
         <v>46</v>
       </c>
-      <c r="AG5" s="6">
+      <c r="AG5" s="5">
         <v>1.7034</v>
       </c>
-      <c r="AH5" s="6">
+      <c r="AH5" s="5">
         <v>0.99</v>
       </c>
-      <c r="AI5" s="1" t="s">
+      <c r="AI5" t="s">
         <v>55</v>
       </c>
-      <c r="AJ5" s="1" t="s">
+      <c r="AJ5" t="s">
         <v>56</v>
       </c>
-      <c r="AK5" s="1" t="s">
+      <c r="AK5" t="s">
         <v>57</v>
       </c>
-      <c r="AL5" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="4">
-        <v>42</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="3">
+        <v>42</v>
+      </c>
+      <c r="H6" s="3">
         <v>19</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="3">
         <v>8</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="3">
         <v>20000000</v>
       </c>
-      <c r="M6" s="6">
-        <v>0.00025</v>
-      </c>
-      <c r="N6" s="4">
+      <c r="M6" s="18">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N6" s="3">
         <v>1024</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="3">
         <v>256</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6" s="3">
         <v>4</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="5">
         <v>0.99</v>
       </c>
-      <c r="R6" s="6">
+      <c r="R6" s="5">
         <v>0.95</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="5">
         <v>0.2</v>
       </c>
-      <c r="T6" s="6">
+      <c r="T6" s="5">
         <v>0.05</v>
       </c>
-      <c r="U6" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="V6" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="W6" s="6">
+      <c r="U6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="V6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="W6" s="5">
         <v>0.3</v>
       </c>
-      <c r="X6" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA6" s="4">
+      <c r="X6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA6" s="3">
         <v>512</v>
       </c>
-      <c r="AB6" s="1" t="s">
+      <c r="AB6" t="s">
         <v>45</v>
       </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AC6" t="s">
         <v>45</v>
       </c>
-      <c r="AD6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE6" s="4">
+      <c r="AD6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE6" s="3">
         <v>12319304</v>
       </c>
-      <c r="AF6" s="1" t="s">
+      <c r="AF6" t="s">
         <v>46</v>
       </c>
-      <c r="AG6" s="6">
+      <c r="AG6" s="5">
         <v>-0.189</v>
       </c>
-      <c r="AH6" s="4">
+      <c r="AH6" s="3">
         <v>0</v>
       </c>
-      <c r="AI6" s="1"/>
-      <c r="AJ6" s="1" t="s">
+      <c r="AJ6" t="s">
         <v>61</v>
       </c>
-      <c r="AK6" s="1" t="s">
+      <c r="AK6" t="s">
         <v>62</v>
       </c>
-      <c r="AL6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>4</v>
       </c>
-      <c r="G7" s="4">
-        <v>42</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="G7" s="3">
+        <v>42</v>
+      </c>
+      <c r="H7" s="3">
         <v>19</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="3">
         <v>8</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="3">
         <v>20000000</v>
       </c>
-      <c r="M7" s="6">
-        <v>0.00025</v>
-      </c>
-      <c r="N7" s="4">
+      <c r="M7" s="18">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N7" s="3">
         <v>1024</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O7" s="3">
         <v>256</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7" s="3">
         <v>4</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q7" s="5">
         <v>0.99</v>
       </c>
-      <c r="R7" s="6">
+      <c r="R7" s="5">
         <v>0.95</v>
       </c>
-      <c r="S7" s="6">
+      <c r="S7" s="5">
         <v>0.2</v>
       </c>
-      <c r="T7" s="6">
+      <c r="T7" s="5">
         <v>0.05</v>
       </c>
-      <c r="U7" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="V7" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="W7" s="6">
+      <c r="U7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="W7" s="5">
         <v>0.3</v>
       </c>
-      <c r="X7" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA7" s="4">
+      <c r="X7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA7" s="3">
         <v>512</v>
       </c>
-      <c r="AB7" s="1" t="s">
+      <c r="AB7" t="s">
         <v>45</v>
       </c>
-      <c r="AC7" s="1" t="s">
+      <c r="AC7" t="s">
         <v>45</v>
       </c>
-      <c r="AD7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE7" s="4">
+      <c r="AD7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE7" s="3">
         <v>12321896</v>
       </c>
-      <c r="AF7" s="1" t="s">
+      <c r="AF7" t="s">
         <v>65</v>
       </c>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="1"/>
-      <c r="AJ7" s="1" t="s">
+      <c r="AG7" s="5"/>
+      <c r="AH7" s="3"/>
+      <c r="AJ7" t="s">
         <v>66</v>
       </c>
-      <c r="AK7" s="1" t="s">
+      <c r="AK7" t="s">
         <v>67</v>
       </c>
-      <c r="AL7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="4">
-        <v>42</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="E8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="3">
+        <v>42</v>
+      </c>
+      <c r="H8" s="3">
         <v>19</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="3">
         <v>8</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="3">
         <v>12000000</v>
       </c>
-      <c r="M8" s="6">
-        <v>0.00025</v>
-      </c>
-      <c r="N8" s="4">
+      <c r="M8" s="18">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N8" s="3">
         <v>1024</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="3">
         <v>256</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8" s="3">
         <v>4</v>
       </c>
-      <c r="Q8" s="6">
+      <c r="Q8" s="5">
         <v>0.99</v>
       </c>
-      <c r="R8" s="6">
+      <c r="R8" s="5">
         <v>0.95</v>
       </c>
-      <c r="S8" s="6">
+      <c r="S8" s="5">
         <v>0.2</v>
       </c>
-      <c r="T8" s="6">
+      <c r="T8" s="5">
         <v>0.05</v>
       </c>
-      <c r="U8" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="V8" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="W8" s="6">
+      <c r="U8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="W8" s="5">
         <v>0.3</v>
       </c>
-      <c r="X8" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA8" s="4">
+      <c r="X8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA8" s="3">
         <v>256</v>
       </c>
-      <c r="AB8" s="1" t="s">
+      <c r="AB8" t="s">
         <v>71</v>
       </c>
-      <c r="AC8" s="1" t="s">
+      <c r="AC8" t="s">
         <v>71</v>
       </c>
-      <c r="AD8" s="9">
+      <c r="AD8" s="8">
         <v>256</v>
       </c>
-      <c r="AE8" s="4">
+      <c r="AE8" s="3">
         <v>24867592</v>
       </c>
-      <c r="AF8" s="1" t="s">
+      <c r="AF8" t="s">
         <v>65</v>
       </c>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="4"/>
-      <c r="AI8" s="1"/>
-      <c r="AJ8" s="1" t="s">
+      <c r="AG8" s="5"/>
+      <c r="AH8" s="3"/>
+      <c r="AJ8" t="s">
         <v>72</v>
       </c>
-      <c r="AK8" s="1" t="s">
+      <c r="AK8" t="s">
         <v>73</v>
       </c>
-      <c r="AL8" s="1" t="s">
+      <c r="AL8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4">
-        <v>42</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="G9" s="3">
+        <v>42</v>
+      </c>
+      <c r="H9" s="3">
         <v>19</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="3">
         <v>8</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="3">
         <v>12000000</v>
       </c>
-      <c r="M9" s="6">
-        <v>0.00025</v>
-      </c>
-      <c r="N9" s="4">
+      <c r="M9" s="18">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N9" s="3">
         <v>1024</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="3">
         <v>256</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9" s="3">
         <v>4</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="5">
         <v>0.99</v>
       </c>
-      <c r="R9" s="6">
+      <c r="R9" s="5">
         <v>0.95</v>
       </c>
-      <c r="S9" s="6">
+      <c r="S9" s="5">
         <v>0.2</v>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="5">
         <v>0.05</v>
       </c>
-      <c r="U9" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="V9" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="W9" s="6">
+      <c r="U9" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="W9" s="5">
         <v>0.3</v>
       </c>
-      <c r="X9" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA9" s="4">
+      <c r="X9" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA9" s="3">
         <v>256</v>
       </c>
-      <c r="AB9" s="1" t="s">
+      <c r="AB9" t="s">
         <v>71</v>
       </c>
-      <c r="AC9" s="1" t="s">
+      <c r="AC9" t="s">
         <v>71</v>
       </c>
-      <c r="AD9" s="9">
+      <c r="AD9" s="8">
         <v>256</v>
       </c>
-      <c r="AE9" s="4">
+      <c r="AE9" s="3">
         <v>24867592</v>
       </c>
-      <c r="AF9" s="1" t="s">
+      <c r="AF9" t="s">
         <v>65</v>
       </c>
-      <c r="AG9" s="10"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="1"/>
-      <c r="AJ9" s="1" t="s">
+      <c r="AJ9" t="s">
         <v>78</v>
       </c>
-      <c r="AK9" s="1"/>
-      <c r="AL9" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
-      <c r="V10" s="13"/>
-      <c r="W10" s="13"/>
-      <c r="X10" s="13"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="12"/>
-      <c r="AF10" s="14" t="s">
+    <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E10" s="10"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
+      <c r="S10" s="12"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="12"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="12"/>
+      <c r="Y10" s="12"/>
+      <c r="Z10" s="12"/>
+      <c r="AA10" s="11"/>
+      <c r="AE10" s="11"/>
+      <c r="AF10" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AG10" s="13">
+      <c r="AG10" s="12">
         <v>-0.189</v>
       </c>
-      <c r="AH10" s="12">
+      <c r="AH10" s="11">
         <v>0</v>
       </c>
-      <c r="AI10" s="14" t="s">
+      <c r="AI10" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AJ10" s="14" t="s">
+      <c r="AJ10" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="AK10" s="14" t="s">
+      <c r="AK10" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AL10" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="12">
-        <v>42</v>
-      </c>
-      <c r="H11" s="12">
+      <c r="E11" s="10"/>
+      <c r="G11" s="11">
+        <v>42</v>
+      </c>
+      <c r="H11" s="11">
         <v>19</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="11">
         <v>8</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="11">
         <v>20000000</v>
       </c>
-      <c r="M11" s="13">
-        <v>0.0001</v>
-      </c>
-      <c r="N11" s="12">
+      <c r="M11" s="19">
+        <v>1E-4</v>
+      </c>
+      <c r="N11" s="11">
         <v>512</v>
       </c>
-      <c r="O11" s="12">
+      <c r="O11" s="11">
         <v>128</v>
       </c>
-      <c r="P11" s="12">
+      <c r="P11" s="11">
         <v>3</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11" s="12">
         <v>0.99</v>
       </c>
-      <c r="R11" s="13">
+      <c r="R11" s="12">
         <v>0.95</v>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="12">
         <v>0.1</v>
       </c>
-      <c r="T11" s="13">
+      <c r="T11" s="12">
         <v>0.01</v>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="11">
         <v>1</v>
       </c>
-      <c r="V11" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="W11" s="13">
+      <c r="V11" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="W11" s="12">
         <v>0.3</v>
       </c>
-      <c r="X11" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="Y11" s="15"/>
-      <c r="Z11" s="15"/>
-      <c r="AA11" s="12">
+      <c r="X11" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="11">
         <v>256</v>
       </c>
-      <c r="AB11" s="14" t="s">
+      <c r="AB11" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="AC11" s="14" t="s">
+      <c r="AC11" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="12">
+      <c r="AE11" s="11">
         <v>24867592</v>
       </c>
-      <c r="AF11" s="14" t="s">
+      <c r="AF11" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AG11" s="13"/>
-      <c r="AH11" s="12">
+      <c r="AG11" s="12"/>
+      <c r="AH11" s="11">
         <v>0</v>
       </c>
-      <c r="AI11" s="1"/>
-      <c r="AJ11" s="1"/>
-      <c r="AK11" s="14" t="s">
+      <c r="AK11" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AL11" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="9">
-        <v>42</v>
-      </c>
-      <c r="H12" s="9">
+      <c r="F12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="8">
+        <v>42</v>
+      </c>
+      <c r="H12" s="8">
         <v>19</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="8">
         <v>8</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="8">
         <v>20000000</v>
       </c>
-      <c r="M12" s="16">
-        <v>0.0001</v>
-      </c>
-      <c r="N12" s="9">
+      <c r="M12" s="20">
+        <v>1E-4</v>
+      </c>
+      <c r="N12" s="8">
         <v>512</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="8">
         <v>128</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="8">
         <v>3</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="15">
         <v>0.99</v>
       </c>
-      <c r="R12" s="16">
+      <c r="R12" s="15">
         <v>0.95</v>
       </c>
-      <c r="S12" s="16">
+      <c r="S12" s="15">
         <v>0.1</v>
       </c>
-      <c r="T12" s="16">
+      <c r="T12" s="15">
         <v>0.01</v>
       </c>
-      <c r="U12" s="9">
+      <c r="U12" s="8">
         <v>1</v>
       </c>
-      <c r="V12" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W12" s="16">
+      <c r="V12" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W12" s="15">
         <v>0.3</v>
       </c>
-      <c r="X12" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA12" s="9">
+      <c r="X12" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA12" s="8">
         <v>256</v>
       </c>
-      <c r="AB12" s="1" t="s">
+      <c r="AB12" t="s">
         <v>71</v>
       </c>
-      <c r="AC12" s="1" t="s">
+      <c r="AC12" t="s">
         <v>71</v>
       </c>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="9">
+      <c r="AE12" s="8">
         <v>24867592</v>
       </c>
-      <c r="AF12" s="1" t="s">
+      <c r="AF12" t="s">
         <v>46</v>
       </c>
-      <c r="AG12" s="16">
-        <v>-0.174</v>
-      </c>
-      <c r="AH12" s="9">
+      <c r="AG12" s="15">
+        <v>-0.17399999999999999</v>
+      </c>
+      <c r="AH12" s="8">
         <v>0</v>
       </c>
-      <c r="AI12" s="1"/>
-      <c r="AJ12" s="1" t="s">
+      <c r="AJ12" t="s">
         <v>86</v>
       </c>
-      <c r="AK12" s="1"/>
-      <c r="AL12" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="9">
-        <v>42</v>
-      </c>
-      <c r="H13" s="9">
+      <c r="F13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="8">
+        <v>42</v>
+      </c>
+      <c r="H13" s="8">
         <v>19</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="8">
         <v>8</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="8">
         <v>20000000</v>
       </c>
-      <c r="M13" s="16">
-        <v>0.0001</v>
-      </c>
-      <c r="N13" s="9">
+      <c r="M13" s="20">
+        <v>1E-4</v>
+      </c>
+      <c r="N13" s="8">
         <v>512</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="8">
         <v>128</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="8">
         <v>3</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="Q13" s="15">
         <v>0.99</v>
       </c>
-      <c r="R13" s="16">
+      <c r="R13" s="15">
         <v>0.95</v>
       </c>
-      <c r="S13" s="16">
+      <c r="S13" s="15">
         <v>0.1</v>
       </c>
-      <c r="T13" s="16">
+      <c r="T13" s="15">
         <v>0.01</v>
       </c>
-      <c r="U13" s="9">
+      <c r="U13" s="8">
         <v>1</v>
       </c>
-      <c r="V13" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W13" s="16">
+      <c r="V13" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W13" s="15">
         <v>0.3</v>
       </c>
-      <c r="X13" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA13" s="9">
+      <c r="X13" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA13" s="8">
         <v>512</v>
       </c>
-      <c r="AB13" s="1" t="s">
+      <c r="AB13" t="s">
         <v>71</v>
       </c>
-      <c r="AC13" s="1" t="s">
+      <c r="AC13" t="s">
         <v>71</v>
       </c>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="9">
+      <c r="AE13" s="8">
         <v>49050632</v>
       </c>
-      <c r="AF13" s="1" t="s">
+      <c r="AF13" t="s">
         <v>46</v>
       </c>
-      <c r="AG13" s="16">
+      <c r="AG13" s="15">
         <v>-0.189</v>
       </c>
-      <c r="AH13" s="9">
+      <c r="AH13" s="8">
         <v>0</v>
       </c>
-      <c r="AI13" s="1"/>
-      <c r="AJ13" s="1" t="s">
+      <c r="AJ13" t="s">
         <v>90</v>
       </c>
-      <c r="AK13" s="1"/>
-      <c r="AL13" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>92</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="9">
-        <v>42</v>
-      </c>
-      <c r="H14" s="9">
+      <c r="F14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="8">
+        <v>42</v>
+      </c>
+      <c r="H14" s="8">
         <v>19</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="8">
         <v>8</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="8">
         <v>20000000</v>
       </c>
-      <c r="M14" s="16">
-        <v>0.0001</v>
-      </c>
-      <c r="N14" s="9">
+      <c r="M14" s="20">
+        <v>1E-4</v>
+      </c>
+      <c r="N14" s="8">
         <v>512</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="8">
         <v>128</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="8">
         <v>3</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="Q14" s="15">
         <v>0.99</v>
       </c>
-      <c r="R14" s="16">
+      <c r="R14" s="15">
         <v>0.95</v>
       </c>
-      <c r="S14" s="16">
+      <c r="S14" s="15">
         <v>0.1</v>
       </c>
-      <c r="T14" s="16">
+      <c r="T14" s="15">
         <v>0.01</v>
       </c>
-      <c r="U14" s="9">
+      <c r="U14" s="8">
         <v>1</v>
       </c>
-      <c r="V14" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W14" s="16">
+      <c r="V14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W14" s="15">
         <v>0.3</v>
       </c>
-      <c r="X14" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA14" s="9">
+      <c r="X14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA14" s="8">
         <v>512</v>
       </c>
-      <c r="AB14" s="1" t="s">
+      <c r="AB14" t="s">
         <v>71</v>
       </c>
-      <c r="AC14" s="1" t="s">
+      <c r="AC14" t="s">
         <v>71</v>
       </c>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="9">
+      <c r="AE14" s="8">
         <v>49050632</v>
       </c>
-      <c r="AF14" s="1" t="s">
+      <c r="AF14" t="s">
         <v>46</v>
       </c>
-      <c r="AG14" s="16">
+      <c r="AG14" s="15">
         <v>-0.189</v>
       </c>
-      <c r="AH14" s="9">
+      <c r="AH14" s="8">
         <v>0</v>
       </c>
-      <c r="AI14" s="1"/>
-      <c r="AJ14" s="1" t="s">
+      <c r="AJ14" t="s">
         <v>94</v>
       </c>
-      <c r="AK14" s="1"/>
-      <c r="AL14" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="9">
-        <v>42</v>
-      </c>
-      <c r="H15" s="9">
+      <c r="F15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="8">
+        <v>42</v>
+      </c>
+      <c r="H15" s="8">
         <v>19</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="8">
         <v>8</v>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="8">
         <v>20000000</v>
       </c>
-      <c r="M15" s="16">
-        <v>0.0001</v>
-      </c>
-      <c r="N15" s="9">
+      <c r="M15" s="20">
+        <v>1E-4</v>
+      </c>
+      <c r="N15" s="8">
         <v>512</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="8">
         <v>128</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="8">
         <v>3</v>
       </c>
-      <c r="Q15" s="16">
+      <c r="Q15" s="15">
         <v>0.99</v>
       </c>
-      <c r="R15" s="16">
+      <c r="R15" s="15">
         <v>0.95</v>
       </c>
-      <c r="S15" s="16">
+      <c r="S15" s="15">
         <v>0.1</v>
       </c>
-      <c r="T15" s="16">
+      <c r="T15" s="15">
         <v>0.01</v>
       </c>
-      <c r="U15" s="9">
+      <c r="U15" s="8">
         <v>1</v>
       </c>
-      <c r="V15" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W15" s="16">
+      <c r="V15" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W15" s="15">
         <v>0.3</v>
       </c>
-      <c r="X15" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA15" s="9">
+      <c r="X15" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA15" s="8">
         <v>512</v>
       </c>
-      <c r="AB15" s="1" t="s">
+      <c r="AB15" t="s">
         <v>71</v>
       </c>
-      <c r="AC15" s="1" t="s">
+      <c r="AC15" t="s">
         <v>71</v>
       </c>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="9">
+      <c r="AE15" s="8">
         <v>48098312</v>
       </c>
-      <c r="AF15" s="1" t="s">
+      <c r="AF15" t="s">
         <v>46</v>
       </c>
-      <c r="AG15" s="16">
+      <c r="AG15" s="15">
         <v>-0.189</v>
       </c>
-      <c r="AH15" s="9">
+      <c r="AH15" s="8">
         <v>0</v>
       </c>
-      <c r="AI15" s="1"/>
-      <c r="AJ15" s="1" t="s">
+      <c r="AJ15" t="s">
         <v>98</v>
       </c>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="9">
-        <v>42</v>
-      </c>
-      <c r="H16" s="9">
+      <c r="F16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="8">
+        <v>42</v>
+      </c>
+      <c r="H16" s="8">
         <v>19</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="8">
         <v>8</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="8">
         <v>20000000</v>
       </c>
-      <c r="M16" s="16">
-        <v>0.0001</v>
-      </c>
-      <c r="N16" s="9">
+      <c r="M16" s="20">
+        <v>1E-4</v>
+      </c>
+      <c r="N16" s="8">
         <v>512</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="8">
         <v>128</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="8">
         <v>3</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="15">
         <v>0.99</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="15">
         <v>0.95</v>
       </c>
-      <c r="S16" s="16">
+      <c r="S16" s="15">
         <v>0.1</v>
       </c>
-      <c r="T16" s="16">
+      <c r="T16" s="15">
         <v>0.01</v>
       </c>
-      <c r="U16" s="9">
+      <c r="U16" s="8">
         <v>1</v>
       </c>
-      <c r="V16" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W16" s="16">
+      <c r="V16" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W16" s="15">
         <v>0.3</v>
       </c>
-      <c r="X16" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA16" s="9">
+      <c r="X16" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA16" s="8">
         <v>512</v>
       </c>
-      <c r="AB16" s="1" t="s">
+      <c r="AB16" t="s">
         <v>71</v>
       </c>
-      <c r="AC16" s="1" t="s">
+      <c r="AC16" t="s">
         <v>71</v>
       </c>
-      <c r="AD16" s="3"/>
-      <c r="AE16" s="9">
+      <c r="AE16" s="8">
         <v>48098312</v>
       </c>
-      <c r="AF16" s="1" t="s">
+      <c r="AF16" t="s">
         <v>46</v>
       </c>
-      <c r="AG16" s="10"/>
-      <c r="AH16" s="9">
+      <c r="AH16" s="8">
         <v>0</v>
       </c>
-      <c r="AI16" s="1"/>
-      <c r="AJ16" s="1"/>
-      <c r="AK16" s="1"/>
-      <c r="AL16" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>102</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="9">
-        <v>42</v>
-      </c>
-      <c r="H17" s="9">
+      <c r="F17" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="8">
+        <v>42</v>
+      </c>
+      <c r="H17" s="8">
         <v>19</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="8">
         <v>8</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="8">
         <v>20000000</v>
       </c>
-      <c r="M17" s="16">
-        <v>0.0001</v>
-      </c>
-      <c r="N17" s="9">
+      <c r="M17" s="20">
+        <v>1E-4</v>
+      </c>
+      <c r="N17" s="8">
         <v>512</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="8">
         <v>128</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="8">
         <v>3</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="Q17" s="15">
         <v>0.99</v>
       </c>
-      <c r="R17" s="16">
+      <c r="R17" s="15">
         <v>0.95</v>
       </c>
-      <c r="S17" s="16">
+      <c r="S17" s="15">
         <v>0.1</v>
       </c>
-      <c r="T17" s="16">
+      <c r="T17" s="15">
         <v>0.01</v>
       </c>
-      <c r="U17" s="9">
+      <c r="U17" s="8">
         <v>1</v>
       </c>
-      <c r="V17" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W17" s="16">
+      <c r="V17" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W17" s="15">
         <v>0.3</v>
       </c>
-      <c r="X17" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y17" s="16">
+      <c r="X17" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y17" s="15">
         <v>0.1</v>
       </c>
-      <c r="Z17" s="16">
+      <c r="Z17" s="15">
         <v>0.1</v>
       </c>
-      <c r="AA17" s="9">
+      <c r="AA17" s="8">
         <v>512</v>
       </c>
-      <c r="AB17" s="1" t="s">
+      <c r="AB17" t="s">
         <v>71</v>
       </c>
-      <c r="AC17" s="1" t="s">
+      <c r="AC17" t="s">
         <v>71</v>
       </c>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="9">
+      <c r="AE17" s="8">
         <v>48098312</v>
       </c>
-      <c r="AF17" s="1" t="s">
+      <c r="AF17" t="s">
         <v>46</v>
       </c>
-      <c r="AG17" s="16">
-        <v>1.9591</v>
-      </c>
-      <c r="AH17" s="16">
+      <c r="AG17" s="15">
+        <v>1.9591000000000001</v>
+      </c>
+      <c r="AH17" s="15">
         <v>0.995</v>
       </c>
-      <c r="AI17" s="1" t="s">
+      <c r="AI17" t="s">
         <v>104</v>
       </c>
-      <c r="AJ17" s="1" t="s">
+      <c r="AJ17" t="s">
         <v>105</v>
       </c>
-      <c r="AK17" s="1"/>
-      <c r="AL17" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="9">
-        <v>42</v>
-      </c>
-      <c r="H18" s="9">
+      <c r="F18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="8">
+        <v>42</v>
+      </c>
+      <c r="H18" s="8">
         <v>19</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="8">
         <v>8</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="8">
         <v>20000000</v>
       </c>
-      <c r="M18" s="16">
-        <v>0.0001</v>
-      </c>
-      <c r="N18" s="9">
+      <c r="M18" s="20">
+        <v>1E-4</v>
+      </c>
+      <c r="N18" s="8">
         <v>512</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="8">
         <v>128</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="8">
         <v>3</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="15">
         <v>0.99</v>
       </c>
-      <c r="R18" s="16">
+      <c r="R18" s="15">
         <v>0.95</v>
       </c>
-      <c r="S18" s="16">
+      <c r="S18" s="15">
         <v>0.1</v>
       </c>
-      <c r="T18" s="16">
+      <c r="T18" s="15">
         <v>0.01</v>
       </c>
-      <c r="U18" s="9">
+      <c r="U18" s="8">
         <v>1</v>
       </c>
-      <c r="V18" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W18" s="16">
+      <c r="V18" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W18" s="15">
         <v>0.3</v>
       </c>
-      <c r="X18" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y18" s="16">
+      <c r="X18" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y18" s="15">
         <v>0.1</v>
       </c>
-      <c r="Z18" s="16">
+      <c r="Z18" s="15">
         <v>0.1</v>
       </c>
-      <c r="AA18" s="9">
+      <c r="AA18" s="8">
         <v>512</v>
       </c>
-      <c r="AB18" s="1" t="s">
+      <c r="AB18" t="s">
         <v>71</v>
       </c>
-      <c r="AC18" s="1" t="s">
+      <c r="AC18" t="s">
         <v>71</v>
       </c>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="9">
+      <c r="AE18" s="8">
         <v>7203848</v>
       </c>
-      <c r="AF18" s="1" t="s">
+      <c r="AF18" t="s">
         <v>46</v>
       </c>
-      <c r="AG18" s="16">
-        <v>-0.099</v>
-      </c>
-      <c r="AH18" s="9">
+      <c r="AG18" s="15">
+        <v>-9.9000000000000005E-2</v>
+      </c>
+      <c r="AH18" s="8">
         <v>0</v>
       </c>
-      <c r="AI18" s="1"/>
-      <c r="AJ18" s="1" t="s">
+      <c r="AJ18" t="s">
         <v>108</v>
       </c>
-      <c r="AK18" s="1"/>
-      <c r="AL18" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="9">
-        <v>42</v>
-      </c>
-      <c r="H19" s="9">
+      <c r="F19" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="8">
+        <v>42</v>
+      </c>
+      <c r="H19" s="8">
         <v>19</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="8">
         <v>8</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="8">
         <v>20000000</v>
       </c>
-      <c r="M19" s="16">
-        <v>0.00025</v>
-      </c>
-      <c r="N19" s="9">
+      <c r="M19" s="20">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N19" s="8">
         <v>1024</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="8">
         <v>256</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="8">
         <v>4</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="15">
         <v>0.99</v>
       </c>
-      <c r="R19" s="16">
+      <c r="R19" s="15">
         <v>0.95</v>
       </c>
-      <c r="S19" s="16">
+      <c r="S19" s="15">
         <v>0.2</v>
       </c>
-      <c r="T19" s="16">
+      <c r="T19" s="15">
         <v>0.05</v>
       </c>
-      <c r="U19" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="V19" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W19" s="16">
+      <c r="U19" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="V19" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W19" s="15">
         <v>0.3</v>
       </c>
-      <c r="X19" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA19" s="9">
+      <c r="X19" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA19" s="8">
         <v>512</v>
       </c>
-      <c r="AB19" s="1" t="s">
+      <c r="AB19" t="s">
         <v>45</v>
       </c>
-      <c r="AC19" s="1" t="s">
+      <c r="AC19" t="s">
         <v>45</v>
       </c>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="9">
+      <c r="AE19" s="8">
         <v>12319304</v>
       </c>
-      <c r="AF19" s="1" t="s">
+      <c r="AF19" t="s">
         <v>46</v>
       </c>
-      <c r="AG19" s="16">
-        <v>1.6668</v>
-      </c>
-      <c r="AH19" s="16">
+      <c r="AG19" s="15">
+        <v>1.6668000000000001</v>
+      </c>
+      <c r="AH19" s="15">
         <v>0.995</v>
       </c>
-      <c r="AI19" s="1" t="s">
+      <c r="AI19" t="s">
         <v>112</v>
       </c>
-      <c r="AJ19" s="1" t="s">
+      <c r="AJ19" t="s">
         <v>113</v>
       </c>
-      <c r="AK19" s="1"/>
-      <c r="AL19" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="9">
-        <v>42</v>
-      </c>
-      <c r="H20" s="9">
+      <c r="F20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="8">
+        <v>42</v>
+      </c>
+      <c r="H20" s="8">
         <v>19</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="8">
         <v>8</v>
       </c>
-      <c r="L20" s="9">
+      <c r="L20" s="8">
         <v>50000000</v>
       </c>
-      <c r="M20" s="16">
-        <v>0.00025</v>
-      </c>
-      <c r="N20" s="9">
+      <c r="M20" s="20">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N20" s="8">
         <v>1024</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="8">
         <v>256</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P20" s="8">
         <v>4</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="15">
         <v>0.99</v>
       </c>
-      <c r="R20" s="16">
+      <c r="R20" s="15">
         <v>0.95</v>
       </c>
-      <c r="S20" s="16">
+      <c r="S20" s="15">
         <v>0.2</v>
       </c>
-      <c r="T20" s="16">
+      <c r="T20" s="15">
         <v>0.05</v>
       </c>
-      <c r="U20" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="V20" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W20" s="16">
+      <c r="U20" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="V20" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W20" s="15">
         <v>0.3</v>
       </c>
-      <c r="X20" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA20" s="9">
+      <c r="X20" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA20" s="8">
         <v>256</v>
       </c>
-      <c r="AB20" s="1" t="s">
+      <c r="AB20" t="s">
         <v>71</v>
       </c>
-      <c r="AC20" s="1" t="s">
+      <c r="AC20" t="s">
         <v>71</v>
       </c>
-      <c r="AD20" s="3"/>
-      <c r="AE20" s="9">
+      <c r="AE20" s="8">
         <v>4420360</v>
       </c>
-      <c r="AF20" s="1" t="s">
+      <c r="AF20" t="s">
         <v>65</v>
       </c>
-      <c r="AG20" s="10"/>
-      <c r="AH20" s="3"/>
-      <c r="AI20" s="1"/>
-      <c r="AJ20" s="1" t="s">
+      <c r="AJ20" t="s">
         <v>117</v>
       </c>
-      <c r="AK20" s="1"/>
-      <c r="AL20" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="9">
-        <v>42</v>
-      </c>
-      <c r="H21" s="9">
+      <c r="F21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="8">
+        <v>42</v>
+      </c>
+      <c r="H21" s="8">
         <v>19</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="8">
         <v>8</v>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="8">
         <v>50000000</v>
       </c>
-      <c r="M21" s="16">
-        <v>0.00025</v>
-      </c>
-      <c r="N21" s="9">
+      <c r="M21" s="20">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N21" s="8">
         <v>1024</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="8">
         <v>256</v>
       </c>
-      <c r="P21" s="9">
+      <c r="P21" s="8">
         <v>4</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="Q21" s="15">
         <v>0.99</v>
       </c>
-      <c r="R21" s="16">
+      <c r="R21" s="15">
         <v>0.95</v>
       </c>
-      <c r="S21" s="16">
+      <c r="S21" s="15">
         <v>0.2</v>
       </c>
-      <c r="T21" s="16">
+      <c r="T21" s="15">
         <v>0.05</v>
       </c>
-      <c r="U21" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="V21" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="W21" s="16">
+      <c r="U21" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="V21" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W21" s="15">
         <v>0.3</v>
       </c>
-      <c r="X21" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="Y21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z21" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA21" s="9">
+      <c r="X21" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA21" s="8">
         <v>256</v>
       </c>
-      <c r="AB21" s="1" t="s">
+      <c r="AB21" t="s">
         <v>71</v>
       </c>
-      <c r="AC21" s="1" t="s">
+      <c r="AC21" t="s">
         <v>71</v>
       </c>
-      <c r="AD21" s="3"/>
-      <c r="AE21" s="9">
+      <c r="AE21" s="8">
         <v>4420360</v>
       </c>
-      <c r="AF21" s="1" t="s">
+      <c r="AF21" t="s">
         <v>65</v>
       </c>
-      <c r="AG21" s="10"/>
-      <c r="AH21" s="3"/>
-      <c r="AI21" s="1"/>
-      <c r="AJ21" s="1" t="s">
+      <c r="AJ21" t="s">
         <v>120</v>
       </c>
-      <c r="AK21" s="1"/>
-      <c r="AL21" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="9">
-        <v>42</v>
-      </c>
-      <c r="H22" s="9">
+      <c r="F22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="8">
+        <v>42</v>
+      </c>
+      <c r="H22" s="8">
         <v>19</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="8">
         <v>8</v>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="8">
         <v>20000000</v>
       </c>
-      <c r="M22" s="9">
-        <v>0.00025</v>
-      </c>
-      <c r="N22" s="9">
+      <c r="M22" s="20">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N22" s="8">
         <v>1024</v>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="8">
         <v>256</v>
       </c>
-      <c r="P22" s="9">
+      <c r="P22" s="8">
         <v>4</v>
       </c>
-      <c r="Q22" s="9">
+      <c r="Q22" s="15">
         <v>0.99</v>
       </c>
-      <c r="R22" s="9">
+      <c r="R22" s="15">
         <v>0.95</v>
       </c>
-      <c r="S22" s="9">
+      <c r="S22" s="15">
         <v>0.2</v>
       </c>
-      <c r="T22" s="9">
+      <c r="T22" s="15">
         <v>0.05</v>
       </c>
-      <c r="U22" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="V22" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="W22" s="9">
+      <c r="U22" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="V22" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W22" s="15">
         <v>0.3</v>
       </c>
-      <c r="X22" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="Y22" s="9">
+      <c r="X22" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA22" s="8">
         <v>256</v>
       </c>
-      <c r="Z22" s="9" t="s">
+      <c r="AB22" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="AA22" s="9" t="s">
+      <c r="AC22" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="AB22" s="9">
+      <c r="AE22" s="8">
         <v>2847496</v>
       </c>
-      <c r="AC22" s="9" t="s">
+      <c r="AF22" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="AD22" s="3"/>
-      <c r="AE22" s="9"/>
-      <c r="AF22" s="9" t="s">
+      <c r="AI22" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="AG22" s="16">
-        <v>0.051</v>
-      </c>
-      <c r="AH22" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="1" t="s">
+      <c r="AJ22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>124</v>
       </c>
-      <c r="AJ22" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="AK22" s="1"/>
-      <c r="AL22" s="1"/>
+      <c r="B23" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" t="s">
+        <v>126</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="8">
+        <v>42</v>
+      </c>
+      <c r="H23" s="8">
+        <v>19</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K23" s="8">
+        <v>8</v>
+      </c>
+      <c r="L23" s="8">
+        <v>20000000</v>
+      </c>
+      <c r="M23" s="20">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="N23" s="8">
+        <v>1024</v>
+      </c>
+      <c r="O23" s="8">
+        <v>256</v>
+      </c>
+      <c r="P23" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="15">
+        <v>0.99</v>
+      </c>
+      <c r="R23" s="15">
+        <v>0.95</v>
+      </c>
+      <c r="S23" s="15">
+        <v>0.2</v>
+      </c>
+      <c r="T23" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="U23" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="V23" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="W23" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="X23" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="Y23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA23" s="8">
+        <v>512</v>
+      </c>
+      <c r="AB23" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC23" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE23" s="8">
+        <v>12319304</v>
+      </c>
+      <c r="AF23" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI23" s="8" t="s">
+        <v>127</v>
+      </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
-      <c r="A23" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="9">
-        <v>42</v>
-      </c>
-      <c r="H23" s="9">
-        <v>19</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="K23" s="9">
-        <v>8</v>
-      </c>
-      <c r="L23" s="9">
-        <v>20000000</v>
-      </c>
-      <c r="M23" s="9">
-        <v>0.00025</v>
-      </c>
-      <c r="N23" s="9">
-        <v>1024</v>
-      </c>
-      <c r="O23" s="9">
-        <v>256</v>
-      </c>
-      <c r="P23" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="R23" s="9">
-        <v>0.95</v>
-      </c>
-      <c r="S23" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="T23" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="U23" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="V23" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="W23" s="9">
-        <v>0.3</v>
-      </c>
-      <c r="X23" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="Y23" s="9">
-        <v>512</v>
-      </c>
-      <c r="Z23" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA23" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB23" s="9">
-        <v>12319304</v>
-      </c>
-      <c r="AC23" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD23" s="3"/>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="9" t="s">
+    <row r="24" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="AG23" s="10"/>
-      <c r="AH23" s="3"/>
-      <c r="AI23" s="1"/>
-      <c r="AJ23" s="1"/>
-      <c r="AK23" s="1"/>
-      <c r="AL23" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
-      <c r="A24" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="9"/>
-      <c r="V24" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="W24" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="X24" s="9"/>
-      <c r="Y24" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="3"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD24" s="3"/>
-      <c r="AE24" s="3"/>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="10"/>
-      <c r="AH24" s="3"/>
-      <c r="AI24" s="1"/>
-      <c r="AJ24" s="1"/>
-      <c r="AK24" s="1"/>
-      <c r="AL24" s="1"/>
+      <c r="B24" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="W24" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="X24" s="8"/>
+      <c r="Y24" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC24" s="16" t="s">
+        <v>128</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/runs/experiments.xlsx
+++ b/runs/experiments.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upcomillas-my.sharepoint.com/personal/202111181_alu_comillas_edu/Documents/ICAI/Master/RLprof/Practicas/MiniGrid_Locked4RoomEnv/runs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_826CE3EED135690DA44FD929FBF3D78DA7B44F91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50799215-A9D6-4CBE-A291-B764F640E064}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_826CE3EED135690DA44FD929FBF3D78DA7B44F91" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC386F70-F216-482B-A739-44B3BCB515CE}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-2840" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="runs" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">runs!$D$1:$D$24</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="127">
   <si>
     <t>run_id</t>
   </si>
@@ -376,15 +379,6 @@
     <t>runs/Apr16_23_31_23/best_model.zip</t>
   </si>
   <si>
-    <t>ppo_partialobs_basereward_Apr18_00_29_11</t>
-  </si>
-  <si>
-    <t>2026-04-18 00:29:11</t>
-  </si>
-  <si>
-    <t>runs/Apr18_00_29_11/best_model.zip</t>
-  </si>
-  <si>
     <t>ppo_partialobs_basereward_Apr18_23_11_20</t>
   </si>
   <si>
@@ -407,6 +401,9 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>6 rooms</t>
   </si>
 </sst>
 </file>
@@ -414,7 +411,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -437,7 +434,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,6 +444,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -484,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -529,16 +550,107 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -556,6 +668,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -849,7 +965,7 @@
   <dimension ref="A1:AL24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.44140625" customWidth="1"/>
     <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
@@ -1744,102 +1860,107 @@
       </c>
     </row>
     <row r="9" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="3">
-        <v>42</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="F9" s="41"/>
+      <c r="G9" s="42">
+        <v>42</v>
+      </c>
+      <c r="H9" s="42">
         <v>19</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="42">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="42">
         <v>12000000</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="58">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="49">
         <v>1024</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="49">
         <v>256</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="49">
         <v>4</v>
       </c>
-      <c r="Q9" s="5">
+      <c r="Q9" s="44">
         <v>0.99</v>
       </c>
-      <c r="R9" s="5">
+      <c r="R9" s="44">
         <v>0.95</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="26">
         <v>0.2</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="26">
         <v>0.05</v>
       </c>
-      <c r="U9" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="V9" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="W9" s="5">
+      <c r="U9" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="V9" s="44">
+        <v>0.5</v>
+      </c>
+      <c r="W9" s="44">
         <v>0.3</v>
       </c>
-      <c r="X9" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="Y9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z9" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="X9" s="44">
+        <v>0.5</v>
+      </c>
+      <c r="Y9" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z9" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA9" s="42">
         <v>256</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AB9" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="AC9" t="s">
+      <c r="AC9" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="AD9" s="8">
+      <c r="AD9" s="45">
         <v>256</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AE9" s="42">
         <v>24867592</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AF9" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AG9" s="46"/>
+      <c r="AH9" s="41"/>
+      <c r="AI9" s="38"/>
+      <c r="AJ9" s="38" t="s">
         <v>78</v>
       </c>
+      <c r="AK9" s="38"/>
     </row>
     <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E10" s="10"/>
@@ -1973,1039 +2094,988 @@
       </c>
     </row>
     <row r="12" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="8">
-        <v>42</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="F12" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="45">
+        <v>42</v>
+      </c>
+      <c r="H12" s="45">
         <v>19</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="J12" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="45">
         <v>8</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="45">
         <v>20000000</v>
       </c>
-      <c r="M12" s="20">
+      <c r="M12" s="24">
         <v>1E-4</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N12" s="23">
         <v>512</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="23">
         <v>128</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="23">
         <v>3</v>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="48">
         <v>0.99</v>
       </c>
-      <c r="R12" s="15">
+      <c r="R12" s="48">
         <v>0.95</v>
       </c>
-      <c r="S12" s="15">
+      <c r="S12" s="25">
         <v>0.1</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="25">
         <v>0.01</v>
       </c>
-      <c r="U12" s="8">
+      <c r="U12" s="23">
         <v>1</v>
       </c>
-      <c r="V12" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W12" s="15">
+      <c r="V12" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="W12" s="48">
         <v>0.3</v>
       </c>
-      <c r="X12" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA12" s="8">
+      <c r="X12" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="Y12" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z12" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA12" s="23">
         <v>256</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AB12" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="AC12" t="s">
+      <c r="AC12" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="AE12" s="8">
+      <c r="AD12" s="27"/>
+      <c r="AE12" s="45">
         <v>24867592</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AF12" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="AG12" s="15">
+      <c r="AG12" s="48">
         <v>-0.17399999999999999</v>
       </c>
-      <c r="AH12" s="8">
+      <c r="AH12" s="45">
         <v>0</v>
       </c>
-      <c r="AJ12" t="s">
+      <c r="AI12" s="38"/>
+      <c r="AJ12" s="38" t="s">
         <v>86</v>
       </c>
+      <c r="AK12" s="38"/>
     </row>
     <row r="13" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="8">
-        <v>42</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="F13" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="45">
+        <v>42</v>
+      </c>
+      <c r="H13" s="45">
         <v>19</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="J13" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="45">
         <v>8</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="45">
         <v>20000000</v>
       </c>
-      <c r="M13" s="20">
+      <c r="M13" s="47">
         <v>1E-4</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="45">
         <v>512</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="45">
         <v>128</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P13" s="45">
         <v>3</v>
       </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="48">
         <v>0.99</v>
       </c>
-      <c r="R13" s="15">
+      <c r="R13" s="48">
         <v>0.95</v>
       </c>
-      <c r="S13" s="15">
+      <c r="S13" s="48">
         <v>0.1</v>
       </c>
-      <c r="T13" s="15">
+      <c r="T13" s="48">
         <v>0.01</v>
       </c>
-      <c r="U13" s="8">
+      <c r="U13" s="45">
         <v>1</v>
       </c>
-      <c r="V13" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W13" s="15">
+      <c r="V13" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="W13" s="48">
         <v>0.3</v>
       </c>
-      <c r="X13" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA13" s="8">
+      <c r="X13" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="Y13" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA13" s="23">
         <v>512</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AB13" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="AC13" t="s">
+      <c r="AC13" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="AE13" s="8">
+      <c r="AD13" s="27"/>
+      <c r="AE13" s="45">
         <v>49050632</v>
       </c>
-      <c r="AF13" t="s">
+      <c r="AF13" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="AG13" s="15">
+      <c r="AG13" s="48">
         <v>-0.189</v>
       </c>
-      <c r="AH13" s="8">
+      <c r="AH13" s="45">
         <v>0</v>
       </c>
-      <c r="AJ13" t="s">
+      <c r="AI13" s="38"/>
+      <c r="AJ13" s="38" t="s">
         <v>90</v>
       </c>
+      <c r="AK13" s="38"/>
     </row>
     <row r="14" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="8">
-        <v>42</v>
-      </c>
-      <c r="H14" s="8">
+      <c r="F14" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="45">
+        <v>42</v>
+      </c>
+      <c r="H14" s="45">
         <v>19</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="J14" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="45">
         <v>8</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="45">
         <v>20000000</v>
       </c>
-      <c r="M14" s="20">
+      <c r="M14" s="47">
         <v>1E-4</v>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="45">
         <v>512</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="45">
         <v>128</v>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="45">
         <v>3</v>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q14" s="48">
         <v>0.99</v>
       </c>
-      <c r="R14" s="15">
+      <c r="R14" s="48">
         <v>0.95</v>
       </c>
-      <c r="S14" s="15">
+      <c r="S14" s="48">
         <v>0.1</v>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="48">
         <v>0.01</v>
       </c>
-      <c r="U14" s="8">
+      <c r="U14" s="45">
         <v>1</v>
       </c>
-      <c r="V14" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W14" s="15">
+      <c r="V14" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="W14" s="48">
         <v>0.3</v>
       </c>
-      <c r="X14" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z14" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA14" s="8">
+      <c r="X14" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="Y14" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z14" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA14" s="23">
         <v>512</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AB14" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="AC14" t="s">
+      <c r="AC14" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="AE14" s="8">
+      <c r="AD14" s="27"/>
+      <c r="AE14" s="45">
         <v>49050632</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AF14" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="AG14" s="15">
+      <c r="AG14" s="48">
         <v>-0.189</v>
       </c>
-      <c r="AH14" s="8">
+      <c r="AH14" s="45">
         <v>0</v>
       </c>
-      <c r="AJ14" t="s">
+      <c r="AI14" s="38"/>
+      <c r="AJ14" s="38" t="s">
         <v>94</v>
       </c>
+      <c r="AK14" s="38"/>
     </row>
     <row r="15" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="8">
-        <v>42</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="F15" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="45">
+        <v>42</v>
+      </c>
+      <c r="H15" s="45">
         <v>19</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="45">
         <v>8</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="45">
         <v>20000000</v>
       </c>
-      <c r="M15" s="20">
+      <c r="M15" s="47">
         <v>1E-4</v>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="45">
         <v>512</v>
       </c>
-      <c r="O15" s="8">
+      <c r="O15" s="45">
         <v>128</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="45">
         <v>3</v>
       </c>
-      <c r="Q15" s="15">
+      <c r="Q15" s="48">
         <v>0.99</v>
       </c>
-      <c r="R15" s="15">
+      <c r="R15" s="48">
         <v>0.95</v>
       </c>
-      <c r="S15" s="15">
+      <c r="S15" s="48">
         <v>0.1</v>
       </c>
-      <c r="T15" s="15">
+      <c r="T15" s="48">
         <v>0.01</v>
       </c>
-      <c r="U15" s="8">
+      <c r="U15" s="45">
         <v>1</v>
       </c>
-      <c r="V15" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W15" s="15">
+      <c r="V15" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="W15" s="48">
         <v>0.3</v>
       </c>
-      <c r="X15" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA15" s="8">
+      <c r="X15" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z15" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA15" s="45">
         <v>512</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AB15" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AC15" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="AE15" s="8">
+      <c r="AD15" s="41"/>
+      <c r="AE15" s="45">
         <v>48098312</v>
       </c>
-      <c r="AF15" t="s">
+      <c r="AF15" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="AG15" s="15">
+      <c r="AG15" s="48">
         <v>-0.189</v>
       </c>
-      <c r="AH15" s="8">
+      <c r="AH15" s="45">
         <v>0</v>
       </c>
-      <c r="AJ15" t="s">
+      <c r="AI15" s="38"/>
+      <c r="AJ15" s="38" t="s">
         <v>98</v>
       </c>
+      <c r="AK15" s="38"/>
     </row>
     <row r="16" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="8">
-        <v>42</v>
-      </c>
-      <c r="H16" s="8">
+      <c r="F16" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="45">
+        <v>42</v>
+      </c>
+      <c r="H16" s="45">
         <v>19</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="45">
         <v>8</v>
       </c>
-      <c r="L16" s="8">
+      <c r="L16" s="45">
         <v>20000000</v>
       </c>
-      <c r="M16" s="20">
+      <c r="M16" s="47">
         <v>1E-4</v>
       </c>
-      <c r="N16" s="8">
+      <c r="N16" s="45">
         <v>512</v>
       </c>
-      <c r="O16" s="8">
+      <c r="O16" s="45">
         <v>128</v>
       </c>
-      <c r="P16" s="8">
+      <c r="P16" s="45">
         <v>3</v>
       </c>
-      <c r="Q16" s="15">
+      <c r="Q16" s="48">
         <v>0.99</v>
       </c>
-      <c r="R16" s="15">
+      <c r="R16" s="48">
         <v>0.95</v>
       </c>
-      <c r="S16" s="15">
+      <c r="S16" s="48">
         <v>0.1</v>
       </c>
-      <c r="T16" s="15">
+      <c r="T16" s="48">
         <v>0.01</v>
       </c>
-      <c r="U16" s="8">
+      <c r="U16" s="45">
         <v>1</v>
       </c>
-      <c r="V16" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W16" s="15">
+      <c r="V16" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="W16" s="48">
         <v>0.3</v>
       </c>
-      <c r="X16" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z16" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA16" s="8">
+      <c r="X16" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="Y16" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA16" s="45">
         <v>512</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AB16" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="AC16" t="s">
+      <c r="AC16" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="AE16" s="8">
+      <c r="AD16" s="41"/>
+      <c r="AE16" s="45">
         <v>48098312</v>
       </c>
-      <c r="AF16" t="s">
+      <c r="AF16" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="AH16" s="8">
+      <c r="AG16" s="46"/>
+      <c r="AH16" s="45">
         <v>0</v>
       </c>
+      <c r="AI16" s="38"/>
+      <c r="AJ16" s="38"/>
+      <c r="AK16" s="38"/>
     </row>
-    <row r="17" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:38" s="50" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="8">
-        <v>42</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="F17" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="53">
+        <v>42</v>
+      </c>
+      <c r="H17" s="53">
         <v>19</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="53">
         <v>8</v>
       </c>
-      <c r="L17" s="8">
+      <c r="L17" s="53">
         <v>20000000</v>
       </c>
-      <c r="M17" s="20">
+      <c r="M17" s="55">
         <v>1E-4</v>
       </c>
-      <c r="N17" s="8">
+      <c r="N17" s="53">
         <v>512</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O17" s="53">
         <v>128</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17" s="53">
         <v>3</v>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="56">
         <v>0.99</v>
       </c>
-      <c r="R17" s="15">
+      <c r="R17" s="56">
         <v>0.95</v>
       </c>
-      <c r="S17" s="15">
+      <c r="S17" s="56">
         <v>0.1</v>
       </c>
-      <c r="T17" s="15">
+      <c r="T17" s="56">
         <v>0.01</v>
       </c>
-      <c r="U17" s="8">
+      <c r="U17" s="53">
         <v>1</v>
       </c>
-      <c r="V17" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W17" s="15">
+      <c r="V17" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="W17" s="56">
         <v>0.3</v>
       </c>
-      <c r="X17" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y17" s="15">
+      <c r="X17" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="Y17" s="56">
         <v>0.1</v>
       </c>
-      <c r="Z17" s="15">
+      <c r="Z17" s="56">
         <v>0.1</v>
       </c>
-      <c r="AA17" s="8">
+      <c r="AA17" s="53">
         <v>512</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AB17" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AC17" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="AE17" s="8">
+      <c r="AD17" s="57"/>
+      <c r="AE17" s="53">
         <v>48098312</v>
       </c>
-      <c r="AF17" t="s">
+      <c r="AF17" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="AG17" s="15">
+      <c r="AG17" s="56">
         <v>1.9591000000000001</v>
       </c>
-      <c r="AH17" s="15">
+      <c r="AH17" s="56">
         <v>0.995</v>
       </c>
-      <c r="AI17" t="s">
+      <c r="AI17" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="AJ17" t="s">
+      <c r="AJ17" s="50" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:38" s="50" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="8">
-        <v>42</v>
-      </c>
-      <c r="H18" s="8">
+      <c r="F18" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="53">
+        <v>42</v>
+      </c>
+      <c r="H18" s="53">
         <v>19</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="J18" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="53">
         <v>8</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="53">
         <v>20000000</v>
       </c>
-      <c r="M18" s="20">
+      <c r="M18" s="55">
         <v>1E-4</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="53">
         <v>512</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="53">
         <v>128</v>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="53">
         <v>3</v>
       </c>
-      <c r="Q18" s="15">
+      <c r="Q18" s="56">
         <v>0.99</v>
       </c>
-      <c r="R18" s="15">
+      <c r="R18" s="56">
         <v>0.95</v>
       </c>
-      <c r="S18" s="15">
+      <c r="S18" s="56">
         <v>0.1</v>
       </c>
-      <c r="T18" s="15">
+      <c r="T18" s="56">
         <v>0.01</v>
       </c>
-      <c r="U18" s="8">
+      <c r="U18" s="53">
         <v>1</v>
       </c>
-      <c r="V18" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W18" s="15">
+      <c r="V18" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="W18" s="56">
         <v>0.3</v>
       </c>
-      <c r="X18" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y18" s="15">
+      <c r="X18" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="Y18" s="56">
         <v>0.1</v>
       </c>
-      <c r="Z18" s="15">
+      <c r="Z18" s="56">
         <v>0.1</v>
       </c>
-      <c r="AA18" s="8">
+      <c r="AA18" s="53">
         <v>512</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AB18" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AC18" s="50" t="s">
         <v>71</v>
       </c>
-      <c r="AE18" s="8">
+      <c r="AD18" s="57"/>
+      <c r="AE18" s="53">
         <v>7203848</v>
       </c>
-      <c r="AF18" t="s">
+      <c r="AF18" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="AG18" s="15">
+      <c r="AG18" s="56">
         <v>-9.9000000000000005E-2</v>
       </c>
-      <c r="AH18" s="8">
+      <c r="AH18" s="53">
         <v>0</v>
       </c>
-      <c r="AJ18" t="s">
+      <c r="AJ18" s="50" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="1:38" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="8">
-        <v>42</v>
-      </c>
-      <c r="H19" s="8">
+      <c r="F19" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="31">
+        <v>42</v>
+      </c>
+      <c r="H19" s="31">
         <v>19</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="31">
         <v>8</v>
       </c>
-      <c r="L19" s="8">
+      <c r="L19" s="31">
         <v>20000000</v>
       </c>
-      <c r="M19" s="20">
+      <c r="M19" s="33">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="N19" s="8">
+      <c r="N19" s="31">
         <v>1024</v>
       </c>
-      <c r="O19" s="8">
+      <c r="O19" s="31">
         <v>256</v>
       </c>
-      <c r="P19" s="8">
+      <c r="P19" s="31">
         <v>4</v>
       </c>
-      <c r="Q19" s="15">
+      <c r="Q19" s="34">
         <v>0.99</v>
       </c>
-      <c r="R19" s="15">
+      <c r="R19" s="34">
         <v>0.95</v>
       </c>
-      <c r="S19" s="15">
+      <c r="S19" s="34">
         <v>0.2</v>
       </c>
-      <c r="T19" s="15">
+      <c r="T19" s="34">
         <v>0.05</v>
       </c>
-      <c r="U19" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="V19" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W19" s="15">
+      <c r="U19" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="V19" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="W19" s="34">
         <v>0.3</v>
       </c>
-      <c r="X19" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA19" s="8">
+      <c r="X19" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="Y19" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z19" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA19" s="31">
         <v>512</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AB19" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AC19" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="AE19" s="8">
+      <c r="AD19" s="36"/>
+      <c r="AE19" s="31">
         <v>12319304</v>
       </c>
-      <c r="AF19" t="s">
+      <c r="AF19" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="AG19" s="15">
+      <c r="AG19" s="34">
         <v>1.6668000000000001</v>
       </c>
-      <c r="AH19" s="15">
+      <c r="AH19" s="34">
         <v>0.995</v>
       </c>
-      <c r="AI19" t="s">
+      <c r="AI19" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="AJ19" t="s">
+      <c r="AJ19" s="28" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:38" s="28" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="8">
-        <v>42</v>
-      </c>
-      <c r="H20" s="8">
+      <c r="F20" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="31">
+        <v>42</v>
+      </c>
+      <c r="H20" s="31">
         <v>19</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="J20" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="K20" s="8">
+      <c r="K20" s="31">
         <v>8</v>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="31">
         <v>50000000</v>
       </c>
-      <c r="M20" s="20">
+      <c r="M20" s="33">
         <v>2.5000000000000001E-4</v>
       </c>
-      <c r="N20" s="8">
+      <c r="N20" s="31">
         <v>1024</v>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="31">
         <v>256</v>
       </c>
-      <c r="P20" s="8">
+      <c r="P20" s="31">
         <v>4</v>
       </c>
-      <c r="Q20" s="15">
+      <c r="Q20" s="34">
         <v>0.99</v>
       </c>
-      <c r="R20" s="15">
+      <c r="R20" s="34">
         <v>0.95</v>
       </c>
-      <c r="S20" s="15">
+      <c r="S20" s="34">
         <v>0.2</v>
       </c>
-      <c r="T20" s="15">
+      <c r="T20" s="34">
         <v>0.05</v>
       </c>
-      <c r="U20" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="V20" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W20" s="15">
+      <c r="U20" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="V20" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="W20" s="34">
         <v>0.3</v>
       </c>
-      <c r="X20" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA20" s="8">
+      <c r="X20" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="Y20" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z20" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA20" s="31">
         <v>256</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AB20" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="AC20" t="s">
+      <c r="AC20" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="AE20" s="8">
+      <c r="AD20" s="36"/>
+      <c r="AE20" s="31">
         <v>4420360</v>
       </c>
-      <c r="AF20" t="s">
+      <c r="AF20" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="AJ20" t="s">
+      <c r="AG20" s="37"/>
+      <c r="AH20" s="36"/>
+      <c r="AJ20" s="28" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:38" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="15"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="8"/>
+      <c r="AE21" s="8"/>
+    </row>
+    <row r="22" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>118</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>119</v>
-      </c>
-      <c r="C21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="8">
-        <v>42</v>
-      </c>
-      <c r="H21" s="8">
-        <v>19</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K21" s="8">
-        <v>8</v>
-      </c>
-      <c r="L21" s="8">
-        <v>50000000</v>
-      </c>
-      <c r="M21" s="20">
-        <v>2.5000000000000001E-4</v>
-      </c>
-      <c r="N21" s="8">
-        <v>1024</v>
-      </c>
-      <c r="O21" s="8">
-        <v>256</v>
-      </c>
-      <c r="P21" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q21" s="15">
-        <v>0.99</v>
-      </c>
-      <c r="R21" s="15">
-        <v>0.95</v>
-      </c>
-      <c r="S21" s="15">
-        <v>0.2</v>
-      </c>
-      <c r="T21" s="15">
-        <v>0.05</v>
-      </c>
-      <c r="U21" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="V21" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="W21" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="X21" s="15">
-        <v>0.5</v>
-      </c>
-      <c r="Y21" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z21" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA21" s="8">
-        <v>256</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>71</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>71</v>
-      </c>
-      <c r="AE21" s="8">
-        <v>4420360</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>65</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" t="s">
-        <v>122</v>
       </c>
       <c r="C22" t="s">
         <v>116</v>
@@ -3095,21 +3165,24 @@
         <v>65</v>
       </c>
       <c r="AI22" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" t="s">
         <v>123</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" t="s">
-        <v>126</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>40</v>
@@ -3199,18 +3272,18 @@
         <v>65</v>
       </c>
       <c r="AI23" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -3230,20 +3303,21 @@
       <c r="T24" s="15"/>
       <c r="U24" s="8"/>
       <c r="V24" s="17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="W24" s="17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="X24" s="8"/>
       <c r="Y24" s="17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="AC24" s="16" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="D1:D24" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/runs/experiments.xlsx
+++ b/runs/experiments.xlsx
@@ -3688,19 +3688,29 @@
           <t>running</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>runs/Apr19_22_20_32/best_model.zip</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>finished</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>runs/Apr19_22_20_32/best_model.zip</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
